--- a/测试数据20260603/测试数据20260603/固定信息表-Employee fixed data template20260603.xlsx
+++ b/测试数据20260603/测试数据20260603/固定信息表-Employee fixed data template20260603.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e16\code\react\kairis-gw\测试数据20260603\测试数据20260603\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D9089E-9644-4070-BB83-D3D0F10CDAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E0CC8A-181D-4FA9-AF39-99950DA5F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11235" xr2:uid="{6B964242-7783-4F55-9B37-964571950F25}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B964242-7783-4F55-9B37-964571950F25}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee fixed data template" sheetId="1" r:id="rId1"/>
@@ -206,16 +206,15 @@
     <t>Finance Senior Officer</t>
   </si>
   <si>
-    <t>djhj@gmail.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Post_Function_alw/Month</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Accommodation_alw/Month</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test@gdap-indo.com</t>
   </si>
 </sst>
 </file>
@@ -774,7 +773,7 @@
         <v>6</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>7</v>
@@ -801,7 +800,7 @@
         <v>14</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>15</v>
@@ -860,7 +859,7 @@
         <v>23870</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L2" s="16">
         <v>5000000</v>
@@ -952,7 +951,7 @@
         <v>29709</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L3" s="17">
         <v>7000000</v>
@@ -1044,7 +1043,7 @@
         <v>33820</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L4" s="17">
         <v>10000000</v>
@@ -1136,7 +1135,7 @@
         <v>23704</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L5" s="17">
         <v>20000000</v>
@@ -1198,10 +1197,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" xr:uid="{CFBDAA5D-CFD1-4685-AE73-26727B6E44E9}"/>
-    <hyperlink ref="K3:K5" r:id="rId2" display="djhj@gmail.com" xr:uid="{5CA3DF17-5DCB-4F18-B9C3-57E9CFFB863A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/测试数据20260603/测试数据20260603/固定信息表-Employee fixed data template20260603.xlsx
+++ b/测试数据20260603/测试数据20260603/固定信息表-Employee fixed data template20260603.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e16\code\react\kairis-gw\测试数据20260603\测试数据20260603\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E0CC8A-181D-4FA9-AF39-99950DA5F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25FECE7-F113-406B-96F6-49E2FE237FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B964242-7783-4F55-9B37-964571950F25}"/>
   </bookViews>
@@ -150,78 +150,77 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>abc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aabbcc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dflj.jlkjl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3456789012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jkjlen,.jlsdfj.jljl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4567890123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TK/0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Office Boy</t>
+  </si>
+  <si>
+    <t>K/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IT &amp; Business Development</t>
+  </si>
+  <si>
+    <t>K/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRD Supervisor</t>
+  </si>
+  <si>
+    <t>TK/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Finance Senior Officer</t>
+  </si>
+  <si>
+    <t>Post_Function_alw/Month</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accommodation_alw/Month</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test@gdap-indo.com</t>
+  </si>
+  <si>
     <t>Head Office Jakarta</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>abc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aabbcc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dflj.jlkjl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3456789012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jkjlen,.jlsdfj.jljl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4567890123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TK/0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Office Boy</t>
-  </si>
-  <si>
-    <t>K/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IT &amp; Business Development</t>
-  </si>
-  <si>
-    <t>K/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HRD Supervisor</t>
-  </si>
-  <si>
-    <t>TK/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Finance Senior Officer</t>
-  </si>
-  <si>
-    <t>Post_Function_alw/Month</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accommodation_alw/Month</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test@gdap-indo.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +288,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -336,7 +341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -390,6 +395,9 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -773,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>7</v>
@@ -800,7 +808,7 @@
         <v>14</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>15</v>
@@ -827,27 +835,27 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="D2" s="8">
         <v>1234567890</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="7">
         <v>0</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H2" s="13">
         <v>45444</v>
@@ -859,7 +867,7 @@
         <v>23870</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L2" s="16">
         <v>5000000</v>
@@ -923,23 +931,23 @@
       <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>28</v>
+      <c r="B3" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="10">
         <v>2345678901</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" s="12">
         <v>0.01</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="15">
         <v>44682</v>
@@ -951,7 +959,7 @@
         <v>29709</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L3" s="17">
         <v>7000000</v>
@@ -1011,27 +1019,27 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>28</v>
+      <c r="B4" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="E4" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" s="12">
         <v>0.04</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4" s="15">
         <v>45842</v>
@@ -1043,7 +1051,7 @@
         <v>33820</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L4" s="17">
         <v>10000000</v>
@@ -1107,23 +1115,23 @@
       <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>28</v>
+      <c r="B5" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="15">
         <v>46174</v>
@@ -1135,7 +1143,7 @@
         <v>23704</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L5" s="17">
         <v>20000000</v>

--- a/测试数据20260603/测试数据20260603/固定信息表-Employee fixed data template20260603.xlsx
+++ b/测试数据20260603/测试数据20260603/固定信息表-Employee fixed data template20260603.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e16\code\react\kairis-gw\测试数据20260603\测试数据20260603\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25FECE7-F113-406B-96F6-49E2FE237FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3118BA-8A39-4DB8-AEF0-EED990BCA72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B964242-7783-4F55-9B37-964571950F25}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{6B964242-7783-4F55-9B37-964571950F25}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee fixed data template" sheetId="1" r:id="rId1"/>
@@ -213,7 +213,8 @@
     <t>test@gdap-indo.com</t>
   </si>
   <si>
-    <t>Head Office Jakarta</t>
+    <t>GW16</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
